--- a/Client/Bin/Resources/Data/xlsx/DT_ComboProfile.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_ComboProfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7C5D39-E13F-4AC9-B455-0D7305AA004B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33ADEA9-ED7B-4138-A496-7C2CA50D5F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-45" windowWidth="29040" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DT_ComboProfile" sheetId="1" r:id="rId1"/>
@@ -600,7 +600,7 @@
     <col min="4" max="4" width="19.5" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="25.125" customWidth="1"/>
     <col min="8" max="8" width="10.25" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="14.375" customWidth="1"/>
@@ -668,10 +668,10 @@
         <v>12</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K2" s="2">
         <v>0</v>
@@ -703,10 +703,10 @@
         <v>12</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2">
         <v>0</v>
@@ -738,10 +738,10 @@
         <v>12</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>10</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2">
         <v>0</v>
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K10" s="4">
         <v>0</v>
@@ -983,10 +983,10 @@
         <v>12</v>
       </c>
       <c r="I11" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J11" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K11" s="4">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>10</v>
       </c>
       <c r="I12" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K12" s="4">
         <v>0</v>
@@ -1053,10 +1053,10 @@
         <v>10</v>
       </c>
       <c r="I13" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J13" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" s="4">
         <v>0</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_ComboProfile.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_ComboProfile.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33ADEA9-ED7B-4138-A496-7C2CA50D5F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF744D8-FFA6-4C6D-BA44-5A8F575AB523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -808,10 +808,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>12</v>
       </c>
       <c r="I7" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" s="3">
         <v>0</v>
@@ -878,10 +878,10 @@
         <v>10</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -913,10 +913,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>

--- a/Client/Bin/Resources/Data/xlsx/DT_ComboProfile.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_ComboProfile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF744D8-FFA6-4C6D-BA44-5A8F575AB523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DF9191-6AAF-4DA3-931E-8EB52BB8C57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="45">
   <si>
     <t>profileName</t>
   </si>
@@ -161,6 +161,18 @@
   </si>
   <si>
     <t>검술형 공중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hitReactionType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -270,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -288,6 +300,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -592,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -605,9 +620,10 @@
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="14.375" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="16.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -641,8 +657,11 @@
       <c r="K1" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -671,13 +690,16 @@
         <v>3</v>
       </c>
       <c r="J2" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -706,13 +728,16 @@
         <v>2</v>
       </c>
       <c r="J3" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -741,13 +766,16 @@
         <v>3</v>
       </c>
       <c r="J4" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
@@ -776,13 +804,16 @@
         <v>4</v>
       </c>
       <c r="J5" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
@@ -808,7 +839,7 @@
         <v>12</v>
       </c>
       <c r="I6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3">
         <v>2</v>
@@ -817,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
@@ -852,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -878,7 +909,7 @@
         <v>10</v>
       </c>
       <c r="I8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3">
         <v>3</v>
@@ -887,7 +918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
@@ -916,13 +947,13 @@
         <v>3</v>
       </c>
       <c r="J9" s="3">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
@@ -957,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>40</v>
       </c>
@@ -992,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>40</v>
       </c>
@@ -1027,7 +1058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>40</v>
       </c>
@@ -1062,7 +1093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>41</v>
       </c>
@@ -1097,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>41</v>
       </c>

--- a/Client/Bin/Resources/Data/xlsx/DT_ComboProfile.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_ComboProfile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DF9191-6AAF-4DA3-931E-8EB52BB8C57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B411177-8160-40C5-BA26-D5A3BB1F6203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="47">
   <si>
     <t>profileName</t>
   </si>
@@ -173,6 +173,14 @@
   </si>
   <si>
     <t>hitReactionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit_Air</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit_Air_Down</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -847,6 +855,9 @@
       <c r="K6" s="3">
         <v>0</v>
       </c>
+      <c r="L6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
@@ -882,6 +893,9 @@
       <c r="K7" s="3">
         <v>0</v>
       </c>
+      <c r="L7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -917,6 +931,9 @@
       <c r="K8" s="3">
         <v>0</v>
       </c>
+      <c r="L8" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -951,6 +968,9 @@
       </c>
       <c r="K9" s="3">
         <v>0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">

--- a/Client/Bin/Resources/Data/xlsx/DT_ComboProfile.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_ComboProfile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B411177-8160-40C5-BA26-D5A3BB1F6203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8374E6E-F168-47FF-B2F3-BF7CE151C060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="53">
   <si>
     <t>profileName</t>
   </si>
@@ -103,85 +103,108 @@
     <t>BigSword_Aerial</t>
   </si>
   <si>
+    <t>격투형 일반</t>
+  </si>
+  <si>
+    <t>격투형 일반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>격투형 공중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>launchPower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>launchUp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>격투형 공중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hand_Aerial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Air_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BigSwrod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Sword_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hitSound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검술형 일반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검술형 공중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hitReactionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit_Air</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit_Air_Down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Attack_SwordAir_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Attack_SwordAir_02</t>
-  </si>
-  <si>
-    <t>격투형 일반</t>
-  </si>
-  <si>
-    <t>격투형 일반</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>격투형 공중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>launchPower</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>launchUp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>격투형 공중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hand_Aerial</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hand</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Air_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BigSwrod</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Sword_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hitSound</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검술형 일반</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검술형 공중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Down</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hitReactionType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hit_Air</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hit_Air_Down</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_SwordAir_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_SwordAir_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hand_Hit.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SwordAttack1.wav</t>
+  </si>
+  <si>
+    <t>SwordAttack2.wav</t>
+  </si>
+  <si>
+    <t>SwordKunaiHit.wav</t>
   </si>
 </sst>
 </file>
@@ -290,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -311,6 +334,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -615,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -657,21 +683,21 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
@@ -700,16 +726,16 @@
       <c r="J2" s="2">
         <v>0</v>
       </c>
-      <c r="K2" s="2">
-        <v>0</v>
+      <c r="K2" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
@@ -738,16 +764,16 @@
       <c r="J3" s="2">
         <v>0</v>
       </c>
-      <c r="K3" s="2">
-        <v>0</v>
+      <c r="K3" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>8</v>
@@ -776,16 +802,16 @@
       <c r="J4" s="2">
         <v>0</v>
       </c>
-      <c r="K4" s="2">
-        <v>0</v>
+      <c r="K4" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>8</v>
@@ -814,16 +840,16 @@
       <c r="J5" s="2">
         <v>0</v>
       </c>
-      <c r="K5" s="2">
-        <v>0</v>
+      <c r="K5" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="L5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>16</v>
@@ -852,16 +878,16 @@
       <c r="J6" s="3">
         <v>2</v>
       </c>
-      <c r="K6" s="3">
-        <v>0</v>
+      <c r="K6" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="L6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>16</v>
@@ -890,16 +916,16 @@
       <c r="J7" s="3">
         <v>3</v>
       </c>
-      <c r="K7" s="3">
-        <v>0</v>
+      <c r="K7" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="L7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>16</v>
@@ -928,22 +954,22 @@
       <c r="J8" s="3">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="L8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="D9" s="3" t="b">
         <v>1</v>
@@ -952,7 +978,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G9" s="3">
         <v>2</v>
@@ -966,16 +992,16 @@
       <c r="J9" s="3">
         <v>-3</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
+      <c r="K9" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="L9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>20</v>
@@ -1004,13 +1030,13 @@
       <c r="J10" s="4">
         <v>5</v>
       </c>
-      <c r="K10" s="4">
-        <v>0</v>
+      <c r="K10" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>20</v>
@@ -1039,19 +1065,19 @@
       <c r="J11" s="4">
         <v>4</v>
       </c>
-      <c r="K11" s="4">
-        <v>0</v>
+      <c r="K11" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>10</v>
@@ -1074,13 +1100,13 @@
       <c r="J12" s="4">
         <v>4</v>
       </c>
-      <c r="K12" s="4">
-        <v>0</v>
+      <c r="K12" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>20</v>
@@ -1095,7 +1121,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G13" s="4">
         <v>3</v>
@@ -1109,13 +1135,13 @@
       <c r="J13" s="4">
         <v>4</v>
       </c>
-      <c r="K13" s="4">
-        <v>0</v>
+      <c r="K13" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>25</v>
@@ -1129,28 +1155,31 @@
       <c r="E14" s="5">
         <v>0</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="5">
-        <v>2</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="F14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="5">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0</v>
+      <c r="I14" s="3">
+        <v>2</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
+      </c>
+      <c r="L14" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>25</v>
@@ -1165,23 +1194,99 @@
         <v>1</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="6">
-        <v>3</v>
-      </c>
-      <c r="H15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>3</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I15" s="6">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
+      <c r="I16" s="3">
+        <v>2</v>
+      </c>
+      <c r="J16" s="3">
+        <v>3</v>
+      </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2</v>
+      </c>
+      <c r="H17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
+        <v>-3</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K18" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H14" xr:uid="{00000000-0009-0000-0000-000000000000}">
